--- a/diseases/d053/2010-2014.xlsx
+++ b/diseases/d053/2010-2014.xlsx
@@ -765,9 +765,6 @@
       <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="Q2" t="n">
-        <v>0</v>
-      </c>
       <c r="R2" t="n">
         <v>0</v>
       </c>
@@ -913,9 +910,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1061,9 +1055,6 @@
       <c r="O4" t="n">
         <v>0</v>
       </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1209,9 +1200,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1357,9 +1345,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -1505,9 +1490,6 @@
       <c r="O7" t="n">
         <v>0</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0</v>
       </c>
@@ -1653,9 +1635,6 @@
       <c r="O8" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0</v>
       </c>
@@ -1801,9 +1780,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -1949,9 +1925,6 @@
       <c r="O10" t="n">
         <v>0</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
@@ -2097,9 +2070,6 @@
       <c r="O11" t="n">
         <v>0</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0</v>
       </c>
@@ -2245,9 +2215,6 @@
       <c r="O12" t="n">
         <v>0</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0</v>
       </c>
@@ -2393,9 +2360,6 @@
       <c r="O13" t="n">
         <v>0</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0</v>
       </c>
@@ -2541,9 +2505,6 @@
       <c r="O14" t="n">
         <v>0</v>
       </c>
-      <c r="Q14" t="n">
-        <v>0</v>
-      </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
@@ -2689,9 +2650,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -2837,9 +2795,6 @@
       <c r="O16" t="n">
         <v>0</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
@@ -2985,9 +2940,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -3133,9 +3085,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -3281,9 +3230,6 @@
       <c r="O19" t="n">
         <v>0</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
@@ -3429,9 +3375,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -3577,9 +3520,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -3725,9 +3665,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -4317,9 +4254,6 @@
       <c r="O26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
       <c r="R26" t="n">
         <v>0</v>
       </c>
@@ -5057,9 +4991,6 @@
       <c r="O31" t="n">
         <v>0</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0</v>
       </c>
@@ -5945,9 +5876,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -6685,9 +6613,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -7573,9 +7498,6 @@
       <c r="O48" t="n">
         <v>0</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0</v>
       </c>
@@ -8313,9 +8235,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -9053,9 +8972,6 @@
       <c r="O58" t="n">
         <v>0</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
@@ -9793,9 +9709,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -10681,9 +10594,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -11421,9 +11331,6 @@
       <c r="O74" t="n">
         <v>0</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0</v>
       </c>
@@ -12161,9 +12068,6 @@
       <c r="O79" t="n">
         <v>0</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0</v>
       </c>
@@ -13049,9 +12953,6 @@
       <c r="O85" t="n">
         <v>0</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0</v>
       </c>
@@ -13789,9 +13690,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -14677,9 +14575,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -15417,9 +15312,6 @@
       <c r="O101" t="n">
         <v>0</v>
       </c>
-      <c r="Q101" t="n">
-        <v>0</v>
-      </c>
       <c r="R101" t="n">
         <v>0</v>
       </c>
@@ -16157,9 +16049,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -17045,9 +16934,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -17785,9 +17671,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -18525,9 +18408,6 @@
       <c r="O122" t="n">
         <v>0</v>
       </c>
-      <c r="Q122" t="n">
-        <v>0</v>
-      </c>
       <c r="R122" t="n">
         <v>0</v>
       </c>
@@ -19265,9 +19145,6 @@
       <c r="O127" t="n">
         <v>0</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0</v>
       </c>
@@ -20153,9 +20030,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -20893,9 +20767,6 @@
       <c r="O138" t="n">
         <v>0</v>
       </c>
-      <c r="Q138" t="n">
-        <v>0</v>
-      </c>
       <c r="R138" t="n">
         <v>0</v>
       </c>
@@ -21781,9 +21652,6 @@
       <c r="O144" t="n">
         <v>0</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0</v>
       </c>
@@ -22521,9 +22389,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -23261,9 +23126,6 @@
       <c r="O154" t="n">
         <v>0</v>
       </c>
-      <c r="Q154" t="n">
-        <v>0</v>
-      </c>
       <c r="R154" t="n">
         <v>0</v>
       </c>
@@ -24149,9 +24011,6 @@
       <c r="O160" t="n">
         <v>0</v>
       </c>
-      <c r="Q160" t="n">
-        <v>0</v>
-      </c>
       <c r="R160" t="n">
         <v>0</v>
       </c>
@@ -24887,9 +24746,6 @@
         <v>0</v>
       </c>
       <c r="O165" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q165" t="n">
         <v>0</v>
       </c>
       <c r="R165" t="n">
